--- a/input/16cut_non.xlsx
+++ b/input/16cut_non.xlsx
@@ -1804,6 +1804,36 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1811,30 +1841,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1843,11 +1849,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -1858,11 +1864,38 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
@@ -1909,40 +1942,22 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="8">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
@@ -1954,145 +1969,136 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="56">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="57">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="38" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="39" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="40" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="41" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="45" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="43" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="44" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
@@ -2101,73 +2107,67 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="40">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="39">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="36">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="30">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="18">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="23">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2639,7 +2639,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="343" t="inlineStr">
+      <c r="A1" s="325" t="inlineStr">
         <is>
           <t>16 граней холодная фиксация</t>
         </is>
@@ -2709,22 +2709,22 @@
           <t>CRYSTAL</t>
         </is>
       </c>
-      <c r="B3" s="338" t="inlineStr">
+      <c r="B3" s="329" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C3" s="303" t="n">
+      <c r="C3" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D3" s="30" t="n">
         <v>590</v>
       </c>
-      <c r="E3" s="311">
+      <c r="E3" s="313">
         <f>25+2+30</f>
         <v/>
       </c>
-      <c r="F3" s="311">
+      <c r="F3" s="313">
         <f>1+1</f>
         <v/>
       </c>
@@ -2737,7 +2737,7 @@
           <t>16cut/Crystal/SS6/Non/001</t>
         </is>
       </c>
-      <c r="I3" s="314" t="inlineStr">
+      <c r="I3" s="302" t="inlineStr">
         <is>
           <t>001</t>
         </is>
@@ -2745,22 +2745,22 @@
     </row>
     <row r="4" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
       <c r="A4" s="429" t="n"/>
-      <c r="B4" s="301" t="inlineStr">
+      <c r="B4" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C4" s="301" t="n">
+      <c r="C4" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D4" s="27" t="n">
         <v>701</v>
       </c>
-      <c r="E4" s="312">
+      <c r="E4" s="314">
         <f>25+12+28</f>
         <v/>
       </c>
-      <c r="F4" s="312">
+      <c r="F4" s="314">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -2777,22 +2777,22 @@
     </row>
     <row r="5" ht="17.25" customHeight="1" thickBot="1" thickTop="1">
       <c r="A5" s="429" t="n"/>
-      <c r="B5" s="336" t="inlineStr">
+      <c r="B5" s="330" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C5" s="301" t="n">
+      <c r="C5" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>755</v>
       </c>
-      <c r="E5" s="312">
+      <c r="E5" s="314">
         <f>25+9</f>
         <v/>
       </c>
-      <c r="F5" s="312">
+      <c r="F5" s="314">
         <f>1+5+1</f>
         <v/>
       </c>
@@ -2820,11 +2820,11 @@
       <c r="D6" s="27" t="n">
         <v>866</v>
       </c>
-      <c r="E6" s="312">
+      <c r="E6" s="314">
         <f>25+2+28</f>
         <v/>
       </c>
-      <c r="F6" s="312">
+      <c r="F6" s="314">
         <f>6+1+1</f>
         <v/>
       </c>
@@ -3050,7 +3050,7 @@
           <t>16cut/Сrystal AB/SS34/Non/001+</t>
         </is>
       </c>
-      <c r="I13" s="315" t="inlineStr">
+      <c r="I13" s="301" t="inlineStr">
         <is>
           <t>001+</t>
         </is>
@@ -3062,12 +3062,12 @@
           <t>NEW AB</t>
         </is>
       </c>
-      <c r="B14" s="338" t="inlineStr">
+      <c r="B14" s="329" t="inlineStr">
         <is>
           <t>SS6</t>
         </is>
       </c>
-      <c r="C14" s="303" t="n">
+      <c r="C14" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D14" s="30" t="n">
@@ -3089,7 +3089,7 @@
           <t>16cut/New AB/SS6/Non/112</t>
         </is>
       </c>
-      <c r="I14" s="315" t="inlineStr">
+      <c r="I14" s="301" t="inlineStr">
         <is>
           <t>112</t>
         </is>
@@ -3097,12 +3097,12 @@
     </row>
     <row r="15" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A15" s="429" t="n"/>
-      <c r="B15" s="301" t="inlineStr">
+      <c r="B15" s="311" t="inlineStr">
         <is>
           <t>SS8</t>
         </is>
       </c>
-      <c r="C15" s="301" t="n">
+      <c r="C15" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D15" s="27" t="n">
@@ -3128,12 +3128,12 @@
     </row>
     <row r="16" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A16" s="429" t="n"/>
-      <c r="B16" s="336" t="inlineStr">
+      <c r="B16" s="330" t="inlineStr">
         <is>
           <t>SS10</t>
         </is>
       </c>
-      <c r="C16" s="301" t="n">
+      <c r="C16" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D16" s="27" t="n">
@@ -3381,7 +3381,7 @@
           <t>16cut/Jet Black/SS16/Non/002</t>
         </is>
       </c>
-      <c r="I23" s="315" t="inlineStr">
+      <c r="I23" s="301" t="inlineStr">
         <is>
           <t>002</t>
         </is>
@@ -3480,27 +3480,27 @@
       <c r="I26" s="432" t="n"/>
     </row>
     <row r="27" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A27" s="303" t="inlineStr">
+      <c r="A27" s="310" t="inlineStr">
         <is>
           <t>JONQUIL</t>
         </is>
       </c>
-      <c r="B27" s="338" t="inlineStr">
+      <c r="B27" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C27" s="303" t="n">
+      <c r="C27" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D27" s="30" t="n">
         <v>1169</v>
       </c>
-      <c r="E27" s="303">
+      <c r="E27" s="310">
         <f>15+25+25</f>
         <v/>
       </c>
-      <c r="F27" s="303" t="n"/>
+      <c r="F27" s="310" t="n"/>
       <c r="G27" s="243">
         <f>E27-F27</f>
         <v/>
@@ -3510,7 +3510,7 @@
           <t>16cut/Jonquil/SS16/Non/007</t>
         </is>
       </c>
-      <c r="I27" s="315" t="inlineStr">
+      <c r="I27" s="301" t="inlineStr">
         <is>
           <t>007</t>
         </is>
@@ -3518,22 +3518,22 @@
     </row>
     <row r="28" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A28" s="433" t="n"/>
-      <c r="B28" s="339" t="inlineStr">
+      <c r="B28" s="331" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C28" s="302" t="n">
+      <c r="C28" s="312" t="n">
         <v>1440</v>
       </c>
       <c r="D28" s="28" t="n">
         <v>1749</v>
       </c>
-      <c r="E28" s="302">
+      <c r="E28" s="312">
         <f>15+5+15+15</f>
         <v/>
       </c>
-      <c r="F28" s="302" t="n"/>
+      <c r="F28" s="312" t="n"/>
       <c r="G28" s="246">
         <f>E28-F28</f>
         <v/>
@@ -3546,27 +3546,27 @@
       <c r="I28" s="432" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A29" s="317" t="inlineStr">
+      <c r="A29" s="319" t="inlineStr">
         <is>
           <t>SMOKED TOPAZ</t>
         </is>
       </c>
-      <c r="B29" s="335" t="inlineStr">
+      <c r="B29" s="346" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C29" s="317" t="n">
+      <c r="C29" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D29" s="26" t="n">
         <v>1169</v>
       </c>
-      <c r="E29" s="317">
+      <c r="E29" s="319">
         <f>5+25+25+25</f>
         <v/>
       </c>
-      <c r="F29" s="317" t="n">
+      <c r="F29" s="319" t="n">
         <v>2</v>
       </c>
       <c r="G29" s="244">
@@ -3578,7 +3578,7 @@
           <t>16cut/Smoked Topaz/SS16/Non/009</t>
         </is>
       </c>
-      <c r="I29" s="315" t="inlineStr">
+      <c r="I29" s="301" t="inlineStr">
         <is>
           <t>009</t>
         </is>
@@ -3586,21 +3586,21 @@
     </row>
     <row r="30" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A30" s="429" t="n"/>
-      <c r="B30" s="336" t="inlineStr">
+      <c r="B30" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C30" s="301" t="n">
+      <c r="C30" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D30" s="27" t="n">
         <v>1749</v>
       </c>
-      <c r="E30" s="301" t="n">
+      <c r="E30" s="311" t="n">
         <v>104</v>
       </c>
-      <c r="F30" s="301">
+      <c r="F30" s="311">
         <f>2+1</f>
         <v/>
       </c>
@@ -3617,21 +3617,21 @@
     </row>
     <row r="31" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A31" s="433" t="n"/>
-      <c r="B31" s="337" t="inlineStr">
+      <c r="B31" s="347" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C31" s="318" t="n">
+      <c r="C31" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D31" s="29" t="n">
         <v>1169</v>
       </c>
-      <c r="E31" s="318" t="n">
+      <c r="E31" s="320" t="n">
         <v>80</v>
       </c>
-      <c r="F31" s="318" t="n">
+      <c r="F31" s="320" t="n">
         <v>2</v>
       </c>
       <c r="G31" s="247">
@@ -3646,26 +3646,26 @@
       <c r="I31" s="432" t="n"/>
     </row>
     <row r="32" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A32" s="338" t="inlineStr">
+      <c r="A32" s="329" t="inlineStr">
         <is>
           <t>Lt. Colorado Topaz</t>
         </is>
       </c>
-      <c r="B32" s="338" t="inlineStr">
+      <c r="B32" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C32" s="303" t="n">
+      <c r="C32" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D32" s="30" t="n">
         <v>1169</v>
       </c>
-      <c r="E32" s="303" t="n">
+      <c r="E32" s="310" t="n">
         <v>84</v>
       </c>
-      <c r="F32" s="303" t="n"/>
+      <c r="F32" s="310" t="n"/>
       <c r="G32" s="243">
         <f>E32-F32</f>
         <v/>
@@ -3675,7 +3675,7 @@
           <t>16cut/Lt.Colorado Topaz/SS16/Non/010</t>
         </is>
       </c>
-      <c r="I32" s="315" t="inlineStr">
+      <c r="I32" s="301" t="inlineStr">
         <is>
           <t>010</t>
         </is>
@@ -3683,21 +3683,21 @@
     </row>
     <row r="33" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A33" s="429" t="n"/>
-      <c r="B33" s="336" t="inlineStr">
+      <c r="B33" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C33" s="301" t="n">
+      <c r="C33" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D33" s="27" t="n">
         <v>1749</v>
       </c>
-      <c r="E33" s="301" t="n">
+      <c r="E33" s="311" t="n">
         <v>102</v>
       </c>
-      <c r="F33" s="301" t="n"/>
+      <c r="F33" s="311" t="n"/>
       <c r="G33" s="245">
         <f>E33-F33</f>
         <v/>
@@ -3711,21 +3711,21 @@
     </row>
     <row r="34" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A34" s="433" t="n"/>
-      <c r="B34" s="339" t="inlineStr">
+      <c r="B34" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C34" s="302" t="n">
+      <c r="C34" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D34" s="28" t="n">
         <v>1169</v>
       </c>
-      <c r="E34" s="302" t="n">
+      <c r="E34" s="312" t="n">
         <v>151</v>
       </c>
-      <c r="F34" s="302" t="n"/>
+      <c r="F34" s="312" t="n"/>
       <c r="G34" s="247">
         <f>E34-F34</f>
         <v/>
@@ -3738,7 +3738,7 @@
       <c r="I34" s="432" t="n"/>
     </row>
     <row r="35" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A35" s="303" t="inlineStr">
+      <c r="A35" s="310" t="inlineStr">
         <is>
           <t>BLACK DIAMOND</t>
         </is>
@@ -3767,7 +3767,7 @@
           <t>16cut/Black Diamond/SS16/Non/021</t>
         </is>
       </c>
-      <c r="I35" s="315" t="inlineStr">
+      <c r="I35" s="301" t="inlineStr">
         <is>
           <t>021</t>
         </is>
@@ -3830,7 +3830,7 @@
       <c r="I37" s="432" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A38" s="317" t="inlineStr">
+      <c r="A38" s="319" t="inlineStr">
         <is>
           <t>Lt. Sapphire</t>
         </is>
@@ -3859,7 +3859,7 @@
           <t>16cut/Lt.Sapphire/SS16/Non/011</t>
         </is>
       </c>
-      <c r="I38" s="315" t="inlineStr">
+      <c r="I38" s="301" t="inlineStr">
         <is>
           <t>011</t>
         </is>
@@ -3922,7 +3922,7 @@
       <c r="I40" s="432" t="n"/>
     </row>
     <row r="41" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A41" s="303" t="inlineStr">
+      <c r="A41" s="310" t="inlineStr">
         <is>
           <t>SAPPHIRE</t>
         </is>
@@ -3954,7 +3954,7 @@
           <t>16cut/Sapphire/SS16/Non/013</t>
         </is>
       </c>
-      <c r="I41" s="315" t="inlineStr">
+      <c r="I41" s="301" t="inlineStr">
         <is>
           <t>013</t>
         </is>
@@ -4023,17 +4023,17 @@
       <c r="I43" s="432" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A44" s="321" t="inlineStr">
+      <c r="A44" s="332" t="inlineStr">
         <is>
           <t>MONTANA</t>
         </is>
       </c>
-      <c r="B44" s="321" t="inlineStr">
+      <c r="B44" s="332" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C44" s="321" t="n">
+      <c r="C44" s="332" t="n">
         <v>1440</v>
       </c>
       <c r="D44" s="26" t="n">
@@ -4052,7 +4052,7 @@
           <t>16cut/Montana/SS16/Non/018</t>
         </is>
       </c>
-      <c r="I44" s="315" t="inlineStr">
+      <c r="I44" s="301" t="inlineStr">
         <is>
           <t>018</t>
         </is>
@@ -4088,12 +4088,12 @@
     </row>
     <row r="46" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A46" s="433" t="n"/>
-      <c r="B46" s="323" t="inlineStr">
+      <c r="B46" s="334" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C46" s="323" t="n">
+      <c r="C46" s="334" t="n">
         <v>288</v>
       </c>
       <c r="D46" s="28" t="n">
@@ -4115,7 +4115,7 @@
       <c r="I46" s="432" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A47" s="324" t="inlineStr">
+      <c r="A47" s="335" t="inlineStr">
         <is>
           <t>CAPRI BLUE</t>
         </is>
@@ -4146,7 +4146,7 @@
           <t>16cut/Capri Blue/SS16/Non/017</t>
         </is>
       </c>
-      <c r="I47" s="315" t="inlineStr">
+      <c r="I47" s="301" t="inlineStr">
         <is>
           <t>017</t>
         </is>
@@ -4213,26 +4213,26 @@
       <c r="I49" s="432" t="n"/>
     </row>
     <row r="50" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A50" s="303" t="inlineStr">
+      <c r="A50" s="310" t="inlineStr">
         <is>
           <t>BLUE ZIRCON</t>
         </is>
       </c>
-      <c r="B50" s="338" t="inlineStr">
+      <c r="B50" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C50" s="303" t="n">
+      <c r="C50" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D50" s="30" t="n">
         <v>1169</v>
       </c>
-      <c r="E50" s="303" t="n">
+      <c r="E50" s="310" t="n">
         <v>80</v>
       </c>
-      <c r="F50" s="303" t="n"/>
+      <c r="F50" s="310" t="n"/>
       <c r="G50" s="244">
         <f>E50-F50</f>
         <v/>
@@ -4242,7 +4242,7 @@
           <t>16cut/Green Zircon/SS16/Non/015</t>
         </is>
       </c>
-      <c r="I50" s="315" t="inlineStr">
+      <c r="I50" s="301" t="inlineStr">
         <is>
           <t>015</t>
         </is>
@@ -4250,21 +4250,21 @@
     </row>
     <row r="51" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A51" s="429" t="n"/>
-      <c r="B51" s="336" t="inlineStr">
+      <c r="B51" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C51" s="301" t="n">
+      <c r="C51" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D51" s="27" t="n">
         <v>1749</v>
       </c>
-      <c r="E51" s="301" t="n">
+      <c r="E51" s="311" t="n">
         <v>99</v>
       </c>
-      <c r="F51" s="301" t="n">
+      <c r="F51" s="311" t="n">
         <v>3</v>
       </c>
       <c r="G51" s="245">
@@ -4280,21 +4280,21 @@
     </row>
     <row r="52" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A52" s="433" t="n"/>
-      <c r="B52" s="339" t="inlineStr">
+      <c r="B52" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C52" s="302" t="n">
+      <c r="C52" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D52" s="28" t="n">
         <v>1169</v>
       </c>
-      <c r="E52" s="302" t="n">
+      <c r="E52" s="312" t="n">
         <v>80</v>
       </c>
-      <c r="F52" s="302" t="n"/>
+      <c r="F52" s="312" t="n"/>
       <c r="G52" s="247">
         <f>E52-F52</f>
         <v/>
@@ -4307,7 +4307,7 @@
       <c r="I52" s="432" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A53" s="329" t="inlineStr">
+      <c r="A53" s="340" t="inlineStr">
         <is>
           <t>INDICOLITE</t>
         </is>
@@ -4336,7 +4336,7 @@
           <t>16cut/Indicolite/SS16/Non/014</t>
         </is>
       </c>
-      <c r="I53" s="315" t="inlineStr">
+      <c r="I53" s="301" t="inlineStr">
         <is>
           <t>014</t>
         </is>
@@ -4399,7 +4399,7 @@
       <c r="I55" s="432" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A56" s="317" t="inlineStr">
+      <c r="A56" s="319" t="inlineStr">
         <is>
           <t>AQUAMARINE</t>
         </is>
@@ -4431,7 +4431,7 @@
           <t>16cut/Aquamarine/SS16/Non/016</t>
         </is>
       </c>
-      <c r="I56" s="315" t="inlineStr">
+      <c r="I56" s="301" t="inlineStr">
         <is>
           <t>016</t>
         </is>
@@ -4500,7 +4500,7 @@
       <c r="I58" s="432" t="n"/>
     </row>
     <row r="59" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A59" s="303" t="inlineStr">
+      <c r="A59" s="310" t="inlineStr">
         <is>
           <t>EMERALD</t>
         </is>
@@ -4532,7 +4532,7 @@
           <t>16cut/Emerald/SS16/Non/026</t>
         </is>
       </c>
-      <c r="I59" s="315" t="inlineStr">
+      <c r="I59" s="301" t="inlineStr">
         <is>
           <t>026</t>
         </is>
@@ -4601,7 +4601,7 @@
       <c r="I61" s="432" t="n"/>
     </row>
     <row r="62" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A62" s="317" t="inlineStr">
+      <c r="A62" s="319" t="inlineStr">
         <is>
           <t>Lt. Peridot</t>
         </is>
@@ -4632,7 +4632,7 @@
           <t>16cut/Lt. Peridot/SS16/Non/024</t>
         </is>
       </c>
-      <c r="I62" s="315" t="inlineStr">
+      <c r="I62" s="301" t="inlineStr">
         <is>
           <t>024</t>
         </is>
@@ -4697,17 +4697,17 @@
       <c r="I64" s="432" t="n"/>
     </row>
     <row r="65" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A65" s="332" t="inlineStr">
+      <c r="A65" s="343" t="inlineStr">
         <is>
           <t>OLIVINE</t>
         </is>
       </c>
-      <c r="B65" s="332" t="inlineStr">
+      <c r="B65" s="343" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C65" s="332" t="n">
+      <c r="C65" s="343" t="n">
         <v>1440</v>
       </c>
       <c r="D65" s="30" t="n">
@@ -4726,7 +4726,7 @@
           <t>16cut/Olivine/SS16/Non/027</t>
         </is>
       </c>
-      <c r="I65" s="315" t="inlineStr">
+      <c r="I65" s="301" t="inlineStr">
         <is>
           <t>027</t>
         </is>
@@ -4734,12 +4734,12 @@
     </row>
     <row r="66" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A66" s="429" t="n"/>
-      <c r="B66" s="333" t="inlineStr">
+      <c r="B66" s="344" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C66" s="333" t="n">
+      <c r="C66" s="344" t="n">
         <v>1440</v>
       </c>
       <c r="D66" s="27" t="n">
@@ -4765,12 +4765,12 @@
     </row>
     <row r="67" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A67" s="433" t="n"/>
-      <c r="B67" s="334" t="inlineStr">
+      <c r="B67" s="345" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C67" s="334" t="n">
+      <c r="C67" s="345" t="n">
         <v>288</v>
       </c>
       <c r="D67" s="28" t="n">
@@ -4795,26 +4795,26 @@
       <c r="I67" s="432" t="n"/>
     </row>
     <row r="68" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A68" s="303" t="inlineStr">
+      <c r="A68" s="310" t="inlineStr">
         <is>
           <t>TANZANITE</t>
         </is>
       </c>
-      <c r="B68" s="338" t="inlineStr">
+      <c r="B68" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C68" s="303" t="n">
+      <c r="C68" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D68" s="30" t="n">
         <v>1169</v>
       </c>
-      <c r="E68" s="303" t="n">
+      <c r="E68" s="310" t="n">
         <v>40</v>
       </c>
-      <c r="F68" s="303" t="n"/>
+      <c r="F68" s="310" t="n"/>
       <c r="G68" s="243">
         <f>E68-F68</f>
         <v/>
@@ -4824,7 +4824,7 @@
           <t>16cut/Tanzanite/SS16/Non/028</t>
         </is>
       </c>
-      <c r="I68" s="315" t="inlineStr">
+      <c r="I68" s="301" t="inlineStr">
         <is>
           <t>028</t>
         </is>
@@ -4832,21 +4832,21 @@
     </row>
     <row r="69" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A69" s="429" t="n"/>
-      <c r="B69" s="336" t="inlineStr">
+      <c r="B69" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C69" s="301" t="n">
+      <c r="C69" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D69" s="27" t="n">
         <v>1749</v>
       </c>
-      <c r="E69" s="301" t="n">
+      <c r="E69" s="311" t="n">
         <v>49</v>
       </c>
-      <c r="F69" s="301" t="n">
+      <c r="F69" s="311" t="n">
         <v>1</v>
       </c>
       <c r="G69" s="245">
@@ -4862,21 +4862,21 @@
     </row>
     <row r="70" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A70" s="433" t="n"/>
-      <c r="B70" s="339" t="inlineStr">
+      <c r="B70" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C70" s="302" t="n">
+      <c r="C70" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D70" s="28" t="n">
         <v>1169</v>
       </c>
-      <c r="E70" s="302" t="n">
+      <c r="E70" s="312" t="n">
         <v>40</v>
       </c>
-      <c r="F70" s="302" t="n"/>
+      <c r="F70" s="312" t="n"/>
       <c r="G70" s="246">
         <f>E70-F70</f>
         <v/>
@@ -4889,26 +4889,26 @@
       <c r="I70" s="432" t="n"/>
     </row>
     <row r="71" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A71" s="335" t="inlineStr">
+      <c r="A71" s="346" t="inlineStr">
         <is>
           <t>AMETHYST</t>
         </is>
       </c>
-      <c r="B71" s="335" t="inlineStr">
+      <c r="B71" s="346" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C71" s="317" t="n">
+      <c r="C71" s="319" t="n">
         <v>1440</v>
       </c>
       <c r="D71" s="26" t="n">
         <v>1169</v>
       </c>
-      <c r="E71" s="317" t="n">
+      <c r="E71" s="319" t="n">
         <v>70</v>
       </c>
-      <c r="F71" s="317" t="n"/>
+      <c r="F71" s="319" t="n"/>
       <c r="G71" s="244">
         <f>E71-F71</f>
         <v/>
@@ -4918,7 +4918,7 @@
           <t>16cut/Amethyst/SS16/Non/023</t>
         </is>
       </c>
-      <c r="I71" s="315" t="inlineStr">
+      <c r="I71" s="301" t="inlineStr">
         <is>
           <t>023</t>
         </is>
@@ -4926,21 +4926,21 @@
     </row>
     <row r="72" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A72" s="429" t="n"/>
-      <c r="B72" s="336" t="inlineStr">
+      <c r="B72" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C72" s="301" t="n">
+      <c r="C72" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D72" s="27" t="n">
         <v>1749</v>
       </c>
-      <c r="E72" s="301" t="n">
+      <c r="E72" s="311" t="n">
         <v>72</v>
       </c>
-      <c r="F72" s="301" t="n">
+      <c r="F72" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G72" s="245">
@@ -4956,21 +4956,21 @@
     </row>
     <row r="73" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A73" s="433" t="n"/>
-      <c r="B73" s="337" t="inlineStr">
+      <c r="B73" s="347" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C73" s="318" t="n">
+      <c r="C73" s="320" t="n">
         <v>288</v>
       </c>
       <c r="D73" s="29" t="n">
         <v>1169</v>
       </c>
-      <c r="E73" s="318" t="n">
+      <c r="E73" s="320" t="n">
         <v>50</v>
       </c>
-      <c r="F73" s="318" t="n">
+      <c r="F73" s="320" t="n">
         <v>1</v>
       </c>
       <c r="G73" s="247">
@@ -4990,12 +4990,12 @@
           <t>Lt. Peach</t>
         </is>
       </c>
-      <c r="B74" s="332" t="inlineStr">
+      <c r="B74" s="343" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C74" s="332" t="n">
+      <c r="C74" s="343" t="n">
         <v>1440</v>
       </c>
       <c r="D74" s="30" t="n">
@@ -5014,7 +5014,7 @@
           <t>16cut/Lt. Peach/SS16/Non/029</t>
         </is>
       </c>
-      <c r="I74" s="315" t="inlineStr">
+      <c r="I74" s="301" t="inlineStr">
         <is>
           <t>029</t>
         </is>
@@ -5022,12 +5022,12 @@
     </row>
     <row r="75" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A75" s="429" t="n"/>
-      <c r="B75" s="333" t="inlineStr">
+      <c r="B75" s="344" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C75" s="333" t="n">
+      <c r="C75" s="344" t="n">
         <v>1440</v>
       </c>
       <c r="D75" s="27" t="n">
@@ -5052,12 +5052,12 @@
     </row>
     <row r="76" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A76" s="431" t="n"/>
-      <c r="B76" s="334" t="inlineStr">
+      <c r="B76" s="345" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C76" s="334" t="n">
+      <c r="C76" s="345" t="n">
         <v>288</v>
       </c>
       <c r="D76" s="28" t="n">
@@ -5079,7 +5079,7 @@
       <c r="I76" s="432" t="n"/>
     </row>
     <row r="77" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A77" s="317" t="inlineStr">
+      <c r="A77" s="319" t="inlineStr">
         <is>
           <t>CITRINE</t>
         </is>
@@ -5108,7 +5108,7 @@
           <t>16cut/Citrine/SS16/Non/035</t>
         </is>
       </c>
-      <c r="I77" s="315" t="inlineStr">
+      <c r="I77" s="301" t="inlineStr">
         <is>
           <t>035</t>
         </is>
@@ -5199,7 +5199,7 @@
           <t>16cut/Hyacinth/SS16/Non/031</t>
         </is>
       </c>
-      <c r="I80" s="315" t="inlineStr">
+      <c r="I80" s="301" t="inlineStr">
         <is>
           <t>031</t>
         </is>
@@ -5268,7 +5268,7 @@
       <c r="I82" s="432" t="n"/>
     </row>
     <row r="83" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A83" s="303" t="inlineStr">
+      <c r="A83" s="310" t="inlineStr">
         <is>
           <t>Lt. Siam</t>
         </is>
@@ -5300,7 +5300,7 @@
           <t>16cut/Lt.Siam/SS16/Non/033</t>
         </is>
       </c>
-      <c r="I83" s="315" t="inlineStr">
+      <c r="I83" s="301" t="inlineStr">
         <is>
           <t>033</t>
         </is>
@@ -5369,7 +5369,7 @@
       <c r="I85" s="432" t="n"/>
     </row>
     <row r="86" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A86" s="303" t="inlineStr">
+      <c r="A86" s="310" t="inlineStr">
         <is>
           <t>SIAM</t>
         </is>
@@ -5401,7 +5401,7 @@
           <t>16cut/Siam/SS16/Non/033+</t>
         </is>
       </c>
-      <c r="I86" s="315" t="inlineStr">
+      <c r="I86" s="301" t="inlineStr">
         <is>
           <t>033+</t>
         </is>
@@ -5440,21 +5440,21 @@
     </row>
     <row r="88" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A88" s="433" t="n"/>
-      <c r="B88" s="339" t="inlineStr">
+      <c r="B88" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C88" s="302" t="n">
+      <c r="C88" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D88" s="28" t="n">
         <v>1224</v>
       </c>
-      <c r="E88" s="302" t="n">
+      <c r="E88" s="312" t="n">
         <v>75</v>
       </c>
-      <c r="F88" s="302">
+      <c r="F88" s="312">
         <f>5+6+2+1+2+1+2</f>
         <v/>
       </c>
@@ -5470,7 +5470,7 @@
       <c r="I88" s="432" t="n"/>
     </row>
     <row r="89" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A89" s="303" t="inlineStr">
+      <c r="A89" s="310" t="inlineStr">
         <is>
           <t>GARNET</t>
         </is>
@@ -5502,7 +5502,7 @@
           <t>16cut/Garnet/SS16/Non/034</t>
         </is>
       </c>
-      <c r="I89" s="315" t="inlineStr">
+      <c r="I89" s="301" t="inlineStr">
         <is>
           <t>034</t>
         </is>
@@ -5569,26 +5569,26 @@
       <c r="I91" s="432" t="n"/>
     </row>
     <row r="92" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A92" s="338" t="inlineStr">
+      <c r="A92" s="329" t="inlineStr">
         <is>
           <t>ROSE</t>
         </is>
       </c>
-      <c r="B92" s="338" t="inlineStr">
+      <c r="B92" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C92" s="303" t="n">
+      <c r="C92" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D92" s="30" t="n">
         <v>1720</v>
       </c>
-      <c r="E92" s="303" t="n">
+      <c r="E92" s="310" t="n">
         <v>37</v>
       </c>
-      <c r="F92" s="303" t="n"/>
+      <c r="F92" s="310" t="n"/>
       <c r="G92" s="243">
         <f>E92-F92</f>
         <v/>
@@ -5598,7 +5598,7 @@
           <t>16cut/Rose/SS16/Non/036</t>
         </is>
       </c>
-      <c r="I92" s="315" t="inlineStr">
+      <c r="I92" s="301" t="inlineStr">
         <is>
           <t>036</t>
         </is>
@@ -5606,21 +5606,21 @@
     </row>
     <row r="93" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A93" s="429" t="n"/>
-      <c r="B93" s="336" t="inlineStr">
+      <c r="B93" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C93" s="301" t="n">
+      <c r="C93" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D93" s="27" t="n">
         <v>2906</v>
       </c>
-      <c r="E93" s="301" t="n">
+      <c r="E93" s="311" t="n">
         <v>46</v>
       </c>
-      <c r="F93" s="301" t="n"/>
+      <c r="F93" s="311" t="n"/>
       <c r="G93" s="245">
         <f>E93-F93</f>
         <v/>
@@ -5634,21 +5634,21 @@
     </row>
     <row r="94" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A94" s="433" t="n"/>
-      <c r="B94" s="339" t="inlineStr">
+      <c r="B94" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C94" s="302" t="n">
+      <c r="C94" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D94" s="28" t="n">
         <v>1720</v>
       </c>
-      <c r="E94" s="302" t="n">
+      <c r="E94" s="312" t="n">
         <v>25</v>
       </c>
-      <c r="F94" s="302" t="n"/>
+      <c r="F94" s="312" t="n"/>
       <c r="G94" s="246">
         <f>E94-F94</f>
         <v/>
@@ -5661,12 +5661,12 @@
       <c r="I94" s="432" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A95" s="303" t="inlineStr">
+      <c r="A95" s="310" t="inlineStr">
         <is>
           <t>Lt. Rose</t>
         </is>
       </c>
-      <c r="B95" s="303" t="inlineStr">
+      <c r="B95" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
@@ -5677,10 +5677,10 @@
       <c r="D95" s="30" t="n">
         <v>1513</v>
       </c>
-      <c r="E95" s="303" t="n">
+      <c r="E95" s="310" t="n">
         <v>40</v>
       </c>
-      <c r="F95" s="303">
+      <c r="F95" s="310">
         <f>2+1+1+1</f>
         <v/>
       </c>
@@ -5693,7 +5693,7 @@
           <t>16cut/Lt.Rose/SS16/Non/038</t>
         </is>
       </c>
-      <c r="I95" s="315" t="inlineStr">
+      <c r="I95" s="301" t="inlineStr">
         <is>
           <t>038</t>
         </is>
@@ -5701,7 +5701,7 @@
     </row>
     <row r="96" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A96" s="429" t="n"/>
-      <c r="B96" s="301" t="inlineStr">
+      <c r="B96" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
@@ -5712,10 +5712,10 @@
       <c r="D96" s="27" t="n">
         <v>2013</v>
       </c>
-      <c r="E96" s="301" t="n">
+      <c r="E96" s="311" t="n">
         <v>49</v>
       </c>
-      <c r="F96" s="301">
+      <c r="F96" s="311">
         <f>2+2+1+1</f>
         <v/>
       </c>
@@ -5732,7 +5732,7 @@
     </row>
     <row r="97" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A97" s="433" t="n"/>
-      <c r="B97" s="302" t="inlineStr">
+      <c r="B97" s="312" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
@@ -5743,10 +5743,10 @@
       <c r="D97" s="29" t="n">
         <v>1513</v>
       </c>
-      <c r="E97" s="318" t="n">
+      <c r="E97" s="320" t="n">
         <v>15</v>
       </c>
-      <c r="F97" s="318">
+      <c r="F97" s="320">
         <f>1+1</f>
         <v/>
       </c>
@@ -5762,26 +5762,26 @@
       <c r="I97" s="432" t="n"/>
     </row>
     <row r="98" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A98" s="303" t="inlineStr">
+      <c r="A98" s="310" t="inlineStr">
         <is>
           <t>FUCHSIA</t>
         </is>
       </c>
-      <c r="B98" s="338" t="inlineStr">
+      <c r="B98" s="329" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C98" s="303" t="n">
+      <c r="C98" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D98" s="30" t="n">
         <v>1776</v>
       </c>
-      <c r="E98" s="303" t="n">
+      <c r="E98" s="310" t="n">
         <v>80</v>
       </c>
-      <c r="F98" s="303">
+      <c r="F98" s="310">
         <f>1+1+1+1</f>
         <v/>
       </c>
@@ -5794,7 +5794,7 @@
           <t>16cut/Fuchsia/SS16/Non/037</t>
         </is>
       </c>
-      <c r="I98" s="315" t="inlineStr">
+      <c r="I98" s="301" t="inlineStr">
         <is>
           <t>037</t>
         </is>
@@ -5802,21 +5802,21 @@
     </row>
     <row r="99" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A99" s="429" t="n"/>
-      <c r="B99" s="336" t="inlineStr">
+      <c r="B99" s="330" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C99" s="301" t="n">
+      <c r="C99" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D99" s="27" t="n">
         <v>2906</v>
       </c>
-      <c r="E99" s="301" t="n">
+      <c r="E99" s="311" t="n">
         <v>99</v>
       </c>
-      <c r="F99" s="301">
+      <c r="F99" s="311">
         <f>1+1+1</f>
         <v/>
       </c>
@@ -5833,21 +5833,21 @@
     </row>
     <row r="100" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A100" s="433" t="n"/>
-      <c r="B100" s="339" t="inlineStr">
+      <c r="B100" s="331" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C100" s="302" t="n">
+      <c r="C100" s="312" t="n">
         <v>288</v>
       </c>
       <c r="D100" s="28" t="n">
         <v>1776</v>
       </c>
-      <c r="E100" s="302" t="n">
+      <c r="E100" s="312" t="n">
         <v>50</v>
       </c>
-      <c r="F100" s="302">
+      <c r="F100" s="312">
         <f>1+1</f>
         <v/>
       </c>
@@ -5863,12 +5863,12 @@
       <c r="I100" s="432" t="n"/>
     </row>
     <row r="101" ht="15.75" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A101" s="311" t="inlineStr">
+      <c r="A101" s="313" t="inlineStr">
         <is>
           <t>GOLDEN SHADOW</t>
         </is>
       </c>
-      <c r="B101" s="303" t="inlineStr">
+      <c r="B101" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
@@ -5879,11 +5879,11 @@
       <c r="D101" s="30" t="n">
         <v>1113</v>
       </c>
-      <c r="E101" s="303">
+      <c r="E101" s="310">
         <f>76+40</f>
         <v/>
       </c>
-      <c r="F101" s="303" t="n">
+      <c r="F101" s="310" t="n">
         <v>2</v>
       </c>
       <c r="G101" s="243">
@@ -5895,7 +5895,7 @@
           <t>16cut/Golden Shadow/SS16/Non/052</t>
         </is>
       </c>
-      <c r="I101" s="315" t="inlineStr">
+      <c r="I101" s="301" t="inlineStr">
         <is>
           <t>052</t>
         </is>
@@ -5903,7 +5903,7 @@
     </row>
     <row r="102" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A102" s="429" t="n"/>
-      <c r="B102" s="301" t="inlineStr">
+      <c r="B102" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
@@ -5914,11 +5914,11 @@
       <c r="D102" s="27" t="n">
         <v>1638</v>
       </c>
-      <c r="E102" s="301">
+      <c r="E102" s="311">
         <f>50+90</f>
         <v/>
       </c>
-      <c r="F102" s="301" t="n">
+      <c r="F102" s="311" t="n">
         <v>2</v>
       </c>
       <c r="G102" s="245">
@@ -5934,7 +5934,7 @@
     </row>
     <row r="103" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A103" s="429" t="n"/>
-      <c r="B103" s="301" t="inlineStr">
+      <c r="B103" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
@@ -5945,10 +5945,10 @@
       <c r="D103" s="27" t="n">
         <v>1113</v>
       </c>
-      <c r="E103" s="301" t="n">
+      <c r="E103" s="311" t="n">
         <v>117</v>
       </c>
-      <c r="F103" s="301">
+      <c r="F103" s="311">
         <f>1+2</f>
         <v/>
       </c>
@@ -5965,7 +5965,7 @@
     </row>
     <row r="104" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A104" s="433" t="n"/>
-      <c r="B104" s="302" t="inlineStr">
+      <c r="B104" s="312" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
@@ -5976,10 +5976,10 @@
       <c r="D104" s="28" t="n">
         <v>1528</v>
       </c>
-      <c r="E104" s="302" t="n">
+      <c r="E104" s="312" t="n">
         <v>120</v>
       </c>
-      <c r="F104" s="302">
+      <c r="F104" s="312">
         <f>1+2</f>
         <v/>
       </c>
@@ -5995,26 +5995,26 @@
       <c r="I104" s="432" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
-      <c r="A105" s="303" t="inlineStr">
+      <c r="A105" s="310" t="inlineStr">
         <is>
           <t>SUNSHINE</t>
         </is>
       </c>
-      <c r="B105" s="303" t="inlineStr">
+      <c r="B105" s="310" t="inlineStr">
         <is>
           <t>SS16</t>
         </is>
       </c>
-      <c r="C105" s="303" t="n">
+      <c r="C105" s="310" t="n">
         <v>1440</v>
       </c>
       <c r="D105" s="26" t="n">
         <v>1335</v>
       </c>
-      <c r="E105" s="317" t="n">
+      <c r="E105" s="319" t="n">
         <v>138</v>
       </c>
-      <c r="F105" s="317" t="n"/>
+      <c r="F105" s="319" t="n"/>
       <c r="G105" s="244">
         <f>E105-F105</f>
         <v/>
@@ -6024,7 +6024,7 @@
           <t>16cut/Fuchsia Shimmer/SS16/Non/062</t>
         </is>
       </c>
-      <c r="I105" s="315" t="inlineStr">
+      <c r="I105" s="301" t="inlineStr">
         <is>
           <t>062</t>
         </is>
@@ -6032,21 +6032,21 @@
     </row>
     <row r="106" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A106" s="429" t="n"/>
-      <c r="B106" s="301" t="inlineStr">
+      <c r="B106" s="311" t="inlineStr">
         <is>
           <t>SS20</t>
         </is>
       </c>
-      <c r="C106" s="301" t="n">
+      <c r="C106" s="311" t="n">
         <v>1440</v>
       </c>
       <c r="D106" s="27" t="n">
         <v>1913</v>
       </c>
-      <c r="E106" s="301" t="n">
+      <c r="E106" s="311" t="n">
         <v>165</v>
       </c>
-      <c r="F106" s="301" t="n">
+      <c r="F106" s="311" t="n">
         <v>3</v>
       </c>
       <c r="G106" s="245">
@@ -6062,21 +6062,21 @@
     </row>
     <row r="107" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A107" s="429" t="n"/>
-      <c r="B107" s="301" t="inlineStr">
+      <c r="B107" s="311" t="inlineStr">
         <is>
           <t>SS30</t>
         </is>
       </c>
-      <c r="C107" s="301" t="n">
+      <c r="C107" s="311" t="n">
         <v>288</v>
       </c>
       <c r="D107" s="27" t="n">
         <v>1335</v>
       </c>
-      <c r="E107" s="301" t="n">
+      <c r="E107" s="311" t="n">
         <v>117</v>
       </c>
-      <c r="F107" s="301" t="n">
+      <c r="F107" s="311" t="n">
         <v>3</v>
       </c>
       <c r="G107" s="245">
@@ -6092,21 +6092,21 @@
     </row>
     <row r="108" ht="16.5" customHeight="1" thickBot="1" thickTop="1">
       <c r="A108" s="433" t="n"/>
-      <c r="B108" s="302" t="inlineStr">
+      <c r="B108" s="312" t="inlineStr">
         <is>
           <t>SS34</t>
         </is>
       </c>
-      <c r="C108" s="302" t="n">
+      <c r="C108" s="312" t="n">
         <v>144</v>
       </c>
       <c r="D108" s="28" t="n">
         <v>1743</v>
       </c>
-      <c r="E108" s="302" t="n">
+      <c r="E108" s="312" t="n">
         <v>119</v>
       </c>
-      <c r="F108" s="302" t="n"/>
+      <c r="F108" s="312" t="n"/>
       <c r="G108" s="246">
         <f>E108-F108</f>
         <v/>
@@ -6161,28 +6161,29 @@
   </sheetData>
   <mergeCells count="61">
     <mergeCell ref="I92:I94"/>
-    <mergeCell ref="I68:I70"/>
     <mergeCell ref="I83:I85"/>
     <mergeCell ref="A29:A31"/>
+    <mergeCell ref="A47:A49"/>
     <mergeCell ref="I38:I40"/>
-    <mergeCell ref="A47:A49"/>
     <mergeCell ref="I98:I100"/>
-    <mergeCell ref="I29:I31"/>
     <mergeCell ref="A32:A34"/>
     <mergeCell ref="A38:A40"/>
+    <mergeCell ref="I29:I31"/>
     <mergeCell ref="I101:I104"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="A68:A70"/>
     <mergeCell ref="A62:A64"/>
-    <mergeCell ref="I59:I61"/>
-    <mergeCell ref="I35:I37"/>
-    <mergeCell ref="I50:I52"/>
-    <mergeCell ref="A14:A22"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="I14:I22"/>
-    <mergeCell ref="A35:A37"/>
     <mergeCell ref="A44:A46"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A59:A61"/>
+    <mergeCell ref="A35:A37"/>
+    <mergeCell ref="A14:A22"/>
+    <mergeCell ref="I59:I61"/>
+    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="I14:I22"/>
+    <mergeCell ref="I35:I37"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="I50:I52"/>
     <mergeCell ref="A105:A108"/>
     <mergeCell ref="I65:I67"/>
     <mergeCell ref="A92:A94"/>
@@ -6191,32 +6192,31 @@
     <mergeCell ref="A98:A100"/>
     <mergeCell ref="I89:I91"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I74:I76"/>
     <mergeCell ref="A101:A104"/>
     <mergeCell ref="A83:A85"/>
+    <mergeCell ref="I74:I76"/>
     <mergeCell ref="A23:A26"/>
+    <mergeCell ref="I23:I26"/>
     <mergeCell ref="I86:I88"/>
-    <mergeCell ref="I23:I26"/>
-    <mergeCell ref="A68:A70"/>
     <mergeCell ref="I77:I79"/>
     <mergeCell ref="I95:I97"/>
     <mergeCell ref="I3:I12"/>
-    <mergeCell ref="I47:I49"/>
     <mergeCell ref="A3:A12"/>
     <mergeCell ref="A65:A67"/>
+    <mergeCell ref="I47:I49"/>
     <mergeCell ref="A41:A43"/>
+    <mergeCell ref="A50:A52"/>
     <mergeCell ref="I41:I43"/>
-    <mergeCell ref="A50:A52"/>
     <mergeCell ref="I32:I34"/>
     <mergeCell ref="I62:I64"/>
     <mergeCell ref="I56:I58"/>
+    <mergeCell ref="A74:A76"/>
     <mergeCell ref="I53:I55"/>
-    <mergeCell ref="A74:A76"/>
     <mergeCell ref="A86:A88"/>
     <mergeCell ref="I105:I108"/>
     <mergeCell ref="A80:A82"/>
     <mergeCell ref="A95:A97"/>
-    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="I68:I70"/>
     <mergeCell ref="A89:A91"/>
     <mergeCell ref="I71:I73"/>
     <mergeCell ref="I27:I28"/>
